--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22387,7 +22405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22431,6 +22449,127 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1989_90_0046 'TJ Lokomotiva Pramet Šumperk' prev→CLUB_S1988_89_0082 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1989_90_0013 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1989_90_0015 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0018</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0018 'Prolínací soutěž' (L15, parent=NODE_S1989_90_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0027</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0027 'KVAL skupina A' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0028</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0028 'KVAL skupina B' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0029</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0029 'KVAL finále' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0042</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0042 'Kvalifikace o případný postup do 1. ČNHL' (L25, parent=NODE_S1989_90_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -27568,8 +27707,6 @@
         </is>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122"/>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
@@ -27649,7 +27786,6 @@
         </is>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
@@ -31316,8 +31452,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -55676,6 +55810,237 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0046</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0046 'TJ Lokomotiva Pramet Šumperk' prev→CLUB_S1988_89_0082 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0013</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0013 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0015</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0015 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0018</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1989_90_0018 'Prolínací soutěž' (L15, parent=NODE_S1989_90_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0027</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1989_90_0027 'KVAL skupina A' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0028</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1989_90_0028 'KVAL skupina B' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0029</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1989_90_0029 'KVAL finále' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0042</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1989_90_0042 'Kvalifikace o případný postup do 1. ČNHL' (L25, parent=NODE_S1989_90_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22405,7 +22405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22455,7 +22455,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1989_90_0046 'TJ Lokomotiva Pramet Šumperk' prev→CLUB_S1988_89_0082 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22467,7 +22467,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1989_90_0013 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22479,7 +22479,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1989_90_0015 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22489,14 +22489,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1989_90_0018</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0018 'Prolínací soutěž' (L15, parent=NODE_S1989_90_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22506,14 +22501,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1989_90_0027</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0027 'KVAL skupina A' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22523,14 +22513,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1989_90_0028</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0028 'KVAL skupina B' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -22540,14 +22525,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S1989_90_0029</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0029 'KVAL finále' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0082 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22557,17 +22537,600 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NODE_S1989_90_0042</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1989_90_0042 'Kvalifikace o případný postup do 1. ČNHL' (L25, parent=NODE_S1989_90_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0291 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Statní Statek Cvikov' → 'Cvikov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -27707,6 +28270,8 @@
         </is>
       </c>
     </row>
+    <row r="121"/>
+    <row r="122"/>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
@@ -27737,6 +28302,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0001</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -27749,6 +28319,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0003</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -27761,6 +28336,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0003</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -27773,6 +28353,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0037</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -27786,6 +28371,7 @@
         </is>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
@@ -30025,12 +30611,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -30403,12 +30989,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -30445,12 +31031,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -30744,12 +31330,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -30959,12 +31545,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -31174,12 +31760,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -31452,6 +32038,8 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -31685,12 +32273,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Praha (Žižkov) = TJ Rudá hvězda Žižkov (Wiki D42 - registr ustavy 04/2026). Patterns: RH Žižkov. city Praha (Žižkov).</t>
+          <t>Praha (Žižkov) = TJ Rudá hvězda Žižkov (Wiki D42 - registr ustavy 04/2026). Patterns: RH Žižkov. city Praha (Žižkov). || TBD: city 'Rudá hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Rudá hvězda Žižkov</t>
+          <t>Žižkov</t>
         </is>
       </c>
     </row>
@@ -32352,12 +32940,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -32436,12 +33024,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -32740,12 +33328,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -32829,12 +33417,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -32997,12 +33585,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -33212,12 +33800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -33521,12 +34109,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -34769,12 +35357,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -36441,12 +37029,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -37000,12 +37588,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -37042,12 +37630,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -37168,12 +37756,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -37252,12 +37840,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -37660,12 +38248,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -37806,12 +38394,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -38323,12 +38911,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38417,12 +39005,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38464,12 +39052,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38511,12 +39099,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -41454,12 +42042,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -42502,12 +43090,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -42754,12 +43342,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -42801,12 +43389,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -42848,12 +43436,12 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou.</t>
+          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou. || TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>ČSAD Hrádek nad Nisou</t>
+          <t>Hrádek nad Nisou</t>
         </is>
       </c>
     </row>
@@ -42895,12 +43483,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor.</t>
+          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor. || TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Crystalex 08 Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -42942,12 +43530,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor.</t>
+          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor. || TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Crystalex 08 Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -43036,12 +43624,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -43083,12 +43671,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -43229,12 +43817,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -43615,12 +44203,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -43662,12 +44250,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Cvikov = TJ Statní Statek Cvikov (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. PARSING CHYBA: 'Statní' = preklep z 'Státní'. city Cvikov.</t>
+          <t>Cvikov = TJ Statní Statek Cvikov (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. PARSING CHYBA: 'Statní' = preklep z 'Státní'. city Cvikov. || TBD: city 'Statní Statek Cvikov' → 'Cvikov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>Statní Statek Cvikov</t>
+          <t>Cvikov</t>
         </is>
       </c>
     </row>
@@ -44473,12 +45061,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -46342,12 +46930,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -46762,12 +47350,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -47884,12 +48472,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -49182,12 +49770,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek. || TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Slezan Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -49476,12 +50064,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -51219,12 +51807,12 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky.</t>
+          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky. || TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>Lokomotiva Nové Zámky</t>
+          <t>Nové Zámky</t>
         </is>
       </c>
     </row>
@@ -51592,12 +52180,12 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>Brezno = TJ Jednota SD Brezno (Wiki D42 - registr ustavy 04/2026). Slovensky/Banskobystricky kraj. **Jednota SD** = Spotrebné družstvo Jednota. city Brezno.</t>
+          <t>Brezno = TJ Jednota SD Brezno (Wiki D42 - registr ustavy 04/2026). Slovensky/Banskobystricky kraj. **Jednota SD** = Spotrebné družstvo Jednota. city Brezno. || TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>Jednota SD Brezno</t>
+          <t>Brezno</t>
         </is>
       </c>
     </row>
@@ -51844,12 +52432,12 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -52059,12 +52647,12 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>Poprad = TJ Štátný majetok Poprad (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **Štátný majetok** = státní statky. city Poprad.</t>
+          <t>Poprad = TJ Štátný majetok Poprad (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **Štátný majetok** = státní statky. city Poprad. || TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>Štátný majetok Poprad</t>
+          <t>Poprad</t>
         </is>
       </c>
     </row>
@@ -52284,12 +52872,12 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -55816,11 +56404,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -55865,21 +56453,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0046</t>
+          <t>CLUB_S1989_90_0009</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0046 'TJ Lokomotiva Pramet Šumperk' prev→CLUB_S1988_89_0082 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -55887,21 +56473,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0013</t>
+          <t>CLUB_S1989_90_0018</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0013 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -55909,21 +56493,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0015</t>
+          <t>CLUB_S1989_90_0019</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0015 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -55931,21 +56513,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1989_90_0018</t>
+          <t>CLUB_S1989_90_0026</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1989_90_0018 'Prolínací soutěž' (L15, parent=NODE_S1989_90_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -55953,21 +56533,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1989_90_0027</t>
+          <t>CLUB_S1989_90_0033</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1989_90_0027 'KVAL skupina A' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -55975,21 +56553,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S1989_90_0028</t>
+          <t>CLUB_S1989_90_0038</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1989_90_0028 'KVAL skupina B' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -55997,21 +56573,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S1989_90_0029</t>
+          <t>CLUB_S1989_90_0046</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1989_90_0029 'KVAL finále' (L35, parent=NODE_S1989_90_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0082 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -56019,24 +56593,1002 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NODE_S1989_90_0042</t>
+          <t>CLUB_S1989_90_0048</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1989_90_0042 'Kvalifikace o případný postup do 1. ČNHL' (L25, parent=NODE_S1989_90_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0291 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0056</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rudá hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0073</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0075</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0082</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0084</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0088</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0091</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0093</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0100</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0129</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0165</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0178</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0179</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0182</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0182</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0184</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0193</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0196</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0207</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0209</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0210</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0211</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0275</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0300</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0306</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0307</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0308</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0309</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0310</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0312</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0313</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0316</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0324</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0325</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Statní Statek Cvikov' → 'Cvikov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0344</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0346</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0360</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0387</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0393</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0397</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0420</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0424</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0455</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0462</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0502</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0511</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0517</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0522</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CLUB_S1989_90_0527</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22405,7 +22405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22455,7 +22455,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22467,7 +22467,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22479,7 +22479,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0082 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22491,7 +22491,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0291 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22503,7 +22503,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22515,7 +22515,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -22527,7 +22527,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0082 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22539,7 +22539,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0291 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22551,7 +22551,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22563,7 +22563,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -22575,7 +22575,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -22587,7 +22587,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -22599,7 +22599,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22611,7 +22611,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -22623,7 +22623,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -22635,7 +22635,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -22647,7 +22647,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -22659,7 +22659,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -22671,7 +22671,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -22683,7 +22683,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -22707,7 +22707,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -22719,7 +22719,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -22731,7 +22731,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -22743,7 +22743,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -22755,7 +22755,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -22767,7 +22767,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -22779,7 +22779,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -22791,7 +22791,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -22803,7 +22803,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -22815,7 +22815,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22827,7 +22827,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -22839,7 +22839,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Statní Statek Cvikov' → 'Cvikov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -22851,7 +22851,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -22863,7 +22863,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -22875,7 +22875,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -22887,7 +22887,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22899,7 +22899,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -22911,7 +22911,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -22923,7 +22923,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -22935,7 +22935,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -22947,7 +22947,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Statní Statek Cvikov' → 'Cvikov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22959,7 +22959,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -22971,7 +22971,7 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -22983,7 +22983,7 @@
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -22995,142 +22995,10 @@
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -23147,7 +23015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23206,6 +23074,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23248,6 +23121,11 @@
           <t>12 týmů: základ + playoff + prolínací soutěž. Mistr: Sparta Praha.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23337,6 +23215,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23384,6 +23267,11 @@
           <t>I.ČNHL: základní část + playoff + O 5.-8.místo + Skupina o 9.-12.místo.</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23468,6 +23356,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23510,6 +23403,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23552,6 +23450,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23594,6 +23497,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23636,6 +23544,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23678,6 +23591,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23720,6 +23638,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23762,6 +23685,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23804,6 +23732,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -23846,6 +23779,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23888,6 +23826,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23930,6 +23873,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23972,6 +23920,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24019,6 +23972,11 @@
           <t>Základní tabulka I.ČNHL.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24061,6 +24019,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24103,6 +24066,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24150,6 +24118,11 @@
           <t>VTJ Tábor byl statutárně "B" tým Dukly Jihlava, proto se nemohl ucházet o účast v 1. CHL. Do prolínací soutěže o 1. CHL tak postoupily Olomouc a Vimperk.</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -24192,6 +24165,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -24234,6 +24212,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -24501,6 +24484,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -24627,6 +24615,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -24669,6 +24662,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -24711,6 +24709,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0036</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -24795,6 +24798,11 @@
           <t>II.ČNHL: 3 skupiny + finále.</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -24837,6 +24845,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0039</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -24879,6 +24892,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -24921,6 +24939,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -24968,6 +24991,11 @@
           <t>Do 1. ČNHL postoupily Sokolov, Hodonín a Racek Pardubice. Z 2. ČNHL nikdo nesestoupil; do 2. ČNHL postoupili přímo všichni vítězové krajských přeborů.</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0042</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -25057,6 +25085,11 @@
           <t>II.SNHL: červená+modrá sk. + fáze.</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0043</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -25099,6 +25132,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0044</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -25141,6 +25179,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0045</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25183,6 +25226,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0046</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -25225,6 +25273,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0047</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -25309,6 +25362,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0049</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -25393,6 +25451,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0051</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -25524,6 +25587,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0054</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25566,6 +25634,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0055</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -25608,6 +25681,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0056</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -25650,6 +25728,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0057</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -25692,6 +25775,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0058</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -25818,6 +25906,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0061</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -25860,6 +25953,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0062</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -25907,6 +26005,11 @@
           <t>kvalifikace o KP II.třídy</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0063</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -25949,6 +26052,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0069</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -25991,6 +26099,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0070</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -26033,6 +26146,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0071</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -26117,6 +26235,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0074</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -26159,6 +26282,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0075</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -26201,6 +26329,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0079</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -26243,6 +26376,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0080</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -26285,6 +26423,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0081</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -26332,6 +26475,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0082</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -26374,6 +26522,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0083</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -26416,6 +26569,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0084</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -26458,6 +26616,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0085</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -26500,6 +26663,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0086</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -26542,6 +26710,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0087</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -26584,6 +26757,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0088</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -26836,6 +27014,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0093</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -26878,6 +27061,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0094</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -26920,6 +27108,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0095</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -26962,6 +27155,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0096</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27004,6 +27202,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0097</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27130,6 +27333,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0100</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -27172,6 +27380,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0101</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -27214,6 +27427,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0102</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -27256,6 +27474,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0103</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -27298,6 +27521,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0104</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -27639,6 +27867,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0112</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -27681,6 +27914,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0113</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -27723,6 +27961,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0114</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -27891,6 +28134,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0117</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -27933,6 +28181,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0118</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -27975,6 +28228,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0119</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -28101,6 +28359,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0122</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -28143,6 +28406,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0125</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -28185,6 +28453,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0126</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -28227,6 +28500,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0127</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -28267,6 +28545,11 @@
       <c r="J120" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0128</t>
         </is>
       </c>
     </row>
@@ -28290,6 +28573,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -28307,6 +28595,11 @@
           <t>NODE_S1989_90_0001</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -28324,6 +28617,11 @@
           <t>NODE_S1989_90_0003</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -28341,6 +28639,11 @@
           <t>NODE_S1989_90_0003</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -28358,6 +28661,11 @@
           <t>NODE_S1989_90_0037</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -28368,6 +28676,11 @@
       <c r="B129" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -30611,12 +30924,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -31031,12 +31344,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -31330,12 +31643,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -31545,12 +31858,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -37029,12 +37342,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -37588,12 +37901,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -37756,12 +38069,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -37840,12 +38153,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -38248,12 +38561,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -46930,12 +47243,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -50064,12 +50377,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -56404,7 +56717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -56458,12 +56771,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0009</t>
+          <t>CLUB_S1989_90_0018</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56478,12 +56791,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0018</t>
+          <t>CLUB_S1989_90_0038</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56498,12 +56811,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0019</t>
+          <t>CLUB_S1989_90_0046</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0082 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56518,12 +56831,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0026</t>
+          <t>CLUB_S1989_90_0048</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0291 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56538,12 +56851,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0033</t>
+          <t>CLUB_S1989_90_0056</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rudá hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56558,12 +56871,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0038</t>
+          <t>CLUB_S1989_90_0073</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56578,12 +56891,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0046</t>
+          <t>CLUB_S1989_90_0075</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0082 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56598,12 +56911,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0048</t>
+          <t>CLUB_S1989_90_0082</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0291 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56618,12 +56931,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0056</t>
+          <t>CLUB_S1989_90_0084</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rudá hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56638,12 +56951,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0073</t>
+          <t>CLUB_S1989_90_0088</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56658,12 +56971,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0075</t>
+          <t>CLUB_S1989_90_0091</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -56678,12 +56991,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0082</t>
+          <t>CLUB_S1989_90_0093</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56698,12 +57011,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0084</t>
+          <t>CLUB_S1989_90_0100</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56718,12 +57031,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0088</t>
+          <t>CLUB_S1989_90_0129</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56738,12 +57051,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0091</t>
+          <t>CLUB_S1989_90_0179</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56758,12 +57071,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0093</t>
+          <t>CLUB_S1989_90_0182</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56778,12 +57091,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0100</t>
+          <t>CLUB_S1989_90_0196</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56798,12 +57111,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0129</t>
+          <t>CLUB_S1989_90_0207</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56818,12 +57131,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0165</t>
+          <t>CLUB_S1989_90_0209</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56838,12 +57151,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0178</t>
+          <t>CLUB_S1989_90_0210</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56858,7 +57171,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0179</t>
+          <t>CLUB_S1989_90_0211</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -56878,12 +57191,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0182</t>
+          <t>CLUB_S1989_90_0275</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56898,12 +57211,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0182</t>
+          <t>CLUB_S1989_90_0300</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56918,12 +57231,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0184</t>
+          <t>CLUB_S1989_90_0306</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56938,12 +57251,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0193</t>
+          <t>CLUB_S1989_90_0307</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56958,12 +57271,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0196</t>
+          <t>CLUB_S1989_90_0308</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56978,12 +57291,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0207</t>
+          <t>CLUB_S1989_90_0309</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56998,12 +57311,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0209</t>
+          <t>CLUB_S1989_90_0310</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57018,12 +57331,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0210</t>
+          <t>CLUB_S1989_90_0312</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57038,12 +57351,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0211</t>
+          <t>CLUB_S1989_90_0313</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57058,12 +57371,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0275</t>
+          <t>CLUB_S1989_90_0316</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57078,12 +57391,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0300</t>
+          <t>CLUB_S1989_90_0324</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57098,12 +57411,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0306</t>
+          <t>CLUB_S1989_90_0325</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Statní Statek Cvikov' → 'Cvikov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57118,12 +57431,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0307</t>
+          <t>CLUB_S1989_90_0344</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57138,12 +57451,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0308</t>
+          <t>CLUB_S1989_90_0346</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -57158,12 +57471,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0309</t>
+          <t>CLUB_S1989_90_0360</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57178,12 +57491,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0310</t>
+          <t>CLUB_S1989_90_0393</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -57198,12 +57511,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0312</t>
+          <t>CLUB_S1989_90_0397</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57218,12 +57531,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0313</t>
+          <t>CLUB_S1989_90_0420</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57238,12 +57551,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0316</t>
+          <t>CLUB_S1989_90_0424</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57258,12 +57571,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0324</t>
+          <t>CLUB_S1989_90_0455</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57278,12 +57591,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0325</t>
+          <t>CLUB_S1989_90_0502</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Statní Statek Cvikov' → 'Cvikov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57298,12 +57611,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0344</t>
+          <t>CLUB_S1989_90_0511</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57318,12 +57631,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0346</t>
+          <t>CLUB_S1989_90_0517</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57338,12 +57651,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0360</t>
+          <t>CLUB_S1989_90_0522</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57358,237 +57671,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0387</t>
+          <t>CLUB_S1989_90_0527</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0393</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0397</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0420</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0424</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0455</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0462</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0502</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0511</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0517</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0522</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0527</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F58"/>
+  <autoFilter ref="A1:F47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13687,7 +13687,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Krajská soutěž / o udržení skupina C / Minerva Boskovice — odstoupila</t>
+          <t>Krajská soutěž / o udržení skupina C</t>
         </is>
       </c>
       <c r="C91" s="2" t="n"/>
@@ -22405,7 +22405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22453,45 +22453,65 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0029</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KVAL</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] Ve finále je první utkání hráno doma. Z této kvalifikace nepostoupil nikdo; počet postupujících závisel na prolínací soutěži o 1. CHL.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] SB Poděbrady — odstoupily</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0082 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[club-fate] Minerva Boskovice — odstoupila (club_id: CLUB_S1989_90_0419)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0291 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22503,7 +22523,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22515,7 +22535,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0082 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -22527,7 +22547,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1988_89_0291 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22539,7 +22559,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22551,7 +22571,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22563,7 +22583,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -22575,7 +22595,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -22587,7 +22607,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -22599,7 +22619,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22611,7 +22631,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -22623,7 +22643,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -22635,7 +22655,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -22647,7 +22667,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -22671,7 +22691,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -22683,7 +22703,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -22707,7 +22727,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -22719,7 +22739,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -22731,7 +22751,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -22743,7 +22763,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -22755,7 +22775,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -22767,7 +22787,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -22779,7 +22799,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -22791,7 +22811,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -22803,7 +22823,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -22815,7 +22835,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22839,7 +22859,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Statní Statek Cvikov' → 'Cvikov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -22851,7 +22871,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -22863,7 +22883,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -22875,7 +22895,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Statní Statek Cvikov' → 'Cvikov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -22887,7 +22907,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22899,7 +22919,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -22911,7 +22931,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -22923,7 +22943,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -22935,7 +22955,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -22947,7 +22967,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'Minerva Boskovice — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22959,7 +22979,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -22971,7 +22991,7 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -22983,7 +23003,7 @@
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -22995,10 +23015,58 @@
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -48570,7 +48638,7 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>Boskovice (Wiki - registr ustavy 04/2026). Jihomoravsky kraj. city Boskovice.</t>
+          <t>Boskovice (Wiki - registr ustavy 04/2026). Jihomoravsky kraj. city Boskovice. || TBD: extrahováno z block_name: 'Minerva Boskovice — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -56717,7 +56785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -57531,12 +57599,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0420</t>
+          <t>CLUB_S1989_90_0419</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>TBD: extrahováno z block_name: 'Minerva Boskovice — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -57551,12 +57619,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0424</t>
+          <t>CLUB_S1989_90_0420</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57571,12 +57639,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0455</t>
+          <t>CLUB_S1989_90_0424</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57591,12 +57659,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0502</t>
+          <t>CLUB_S1989_90_0455</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57611,12 +57679,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0511</t>
+          <t>CLUB_S1989_90_0502</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57631,12 +57699,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0517</t>
+          <t>CLUB_S1989_90_0511</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57651,12 +57719,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLUB_S1989_90_0522</t>
+          <t>CLUB_S1989_90_0517</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57671,17 +57739,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>CLUB_S1989_90_0522</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>CLUB_S1989_90_0527</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F47"/>
+  <autoFilter ref="A1:F48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -64212,7 +64300,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Kvalifikace o případný postup do 2. ČNHL / finále / Ve finále je první utkání hráno doma. Z této kvalifikace nepostoupil nikdo; počet postupujících závisel na prolínací soutěži o 1. CHL.</t>
+          <t>Kvalifikace o případný postup do 2. ČNHL / finále</t>
         </is>
       </c>
       <c r="C15" s="2" t="n"/>
@@ -67136,7 +67224,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / SB Poděbrady — odstoupily</t>
+          <t>Krajský přebor</t>
         </is>
       </c>
       <c r="C10" s="2" t="n"/>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -55277,7 +55277,7 @@
         <v>60</v>
       </c>
       <c r="M33" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -55338,10 +55338,10 @@
         <v>6</v>
       </c>
       <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
         <v>4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>62</v>
@@ -55433,7 +55433,7 @@
         <v>62</v>
       </c>
       <c r="M35" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -55511,7 +55511,7 @@
         <v>56</v>
       </c>
       <c r="M36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -32419,8 +32419,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -23083,7 +23083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:N135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23147,6 +23147,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28621,8 +28631,6 @@
         </is>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122"/>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
@@ -28752,7 +28760,6 @@
         </is>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -23424,6 +23424,16 @@
           <t>NODE_S1989_90_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0014</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23438,6 +23448,14 @@
         <is>
           <t>NODE_S1988_89_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -23518,6 +23536,16 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0017</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23532,6 +23560,14 @@
         <is>
           <t>NODE_S1988_89_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -23565,6 +23601,16 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0013</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0012</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23579,6 +23625,14 @@
         <is>
           <t>NODE_S1988_89_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -23612,6 +23666,8 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23626,6 +23682,14 @@
         <is>
           <t>NODE_S1988_89_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -23659,6 +23723,8 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23673,6 +23739,14 @@
         <is>
           <t>NODE_S1988_89_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -23706,6 +23780,8 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23720,6 +23796,14 @@
         <is>
           <t>NODE_S1988_89_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -23753,6 +23837,8 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23767,6 +23853,14 @@
         <is>
           <t>NODE_S1988_89_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -23800,6 +23894,8 @@
           <t>NODE_S1989_90_0001</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23814,6 +23910,14 @@
         <is>
           <t>NODE_S1988_89_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -23847,6 +23951,8 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23861,6 +23967,14 @@
         <is>
           <t>NODE_S1988_89_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -23894,6 +24008,8 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23908,6 +24024,14 @@
         <is>
           <t>NODE_S1988_89_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -23941,6 +24065,16 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0011</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0010</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23955,6 +24089,14 @@
         <is>
           <t>NODE_S1988_89_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -24035,6 +24177,12 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0020</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24054,6 +24202,14 @@
         <is>
           <t>NODE_S1988_89_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -24087,6 +24243,16 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0021</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0024</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24101,6 +24267,14 @@
         <is>
           <t>NODE_S1988_89_0020</t>
         </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -24134,6 +24308,16 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0022</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0023</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24148,6 +24332,14 @@
         <is>
           <t>NODE_S1988_89_0021</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -24181,6 +24373,8 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24200,6 +24394,14 @@
         <is>
           <t>NODE_S1988_89_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -24233,6 +24435,8 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24247,6 +24451,14 @@
         <is>
           <t>NODE_S1988_89_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -24280,6 +24492,8 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24294,6 +24508,14 @@
         <is>
           <t>NODE_S1988_89_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -24327,6 +24549,8 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24341,6 +24565,14 @@
         <is>
           <t>Skupina o 9.-12.místo. 32. kolo: Milevsko – Písek 5:5 bylo kontumováno 0:5 kvůli neoprávněnému startu Luboše Thüra.</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -24505,6 +24737,8 @@
           <t>NODE_S1989_90_0026</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24519,6 +24753,14 @@
         <is>
           <t>Baník Příbram – TJ Spartak Nové Město nad Metují 6:6, 3:6. Ve finále je první utkání hráno doma.</t>
         </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -24777,6 +25019,8 @@
           <t>NODE_S1989_90_0030</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24791,6 +25035,14 @@
         <is>
           <t>NODE_S1988_89_0036</t>
         </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -24824,6 +25076,8 @@
           <t>NODE_S1989_90_0030</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24833,6 +25087,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -25054,6 +25316,8 @@
           <t>NODE_S1989_90_0037</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25073,6 +25337,14 @@
         <is>
           <t>NODE_S1988_89_0042</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -25341,6 +25613,8 @@
           <t>NODE_S1989_90_0044</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25355,6 +25629,14 @@
         <is>
           <t>NODE_S1988_89_0047</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -25388,6 +25670,8 @@
           <t>NODE_S1989_90_0044</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25397,6 +25681,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -25430,6 +25722,8 @@
           <t>NODE_S1989_90_0046</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25444,6 +25738,14 @@
         <is>
           <t>NODE_S1988_89_0049</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -25477,6 +25779,8 @@
           <t>NODE_S1989_90_0046</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25486,6 +25790,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -25519,6 +25831,8 @@
           <t>NODE_S1989_90_0045</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25533,6 +25847,14 @@
         <is>
           <t>NODE_S1988_89_0051</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -25566,6 +25888,8 @@
           <t>NODE_S1989_90_0045</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25575,6 +25899,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -25608,6 +25940,8 @@
           <t>NODE_S1989_90_0043</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25622,6 +25956,14 @@
         <is>
           <t>Finálová skupina II. SNHL. Chybí výsledky prvního a čtvrtého víkendového dvojkola; ve zdroji je v těchto případech uvedeno jen souhrnné skóre a bodový zisk.</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -25650,6 +25992,12 @@
           <t>REG_STC</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0057</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25669,6 +26017,14 @@
         <is>
           <t>NODE_S1988_89_0054</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -25796,6 +26152,8 @@
           <t>NODE_S1989_90_0054</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25810,6 +26168,14 @@
         <is>
           <t>NODE_S1988_89_0057</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>-1.–7. ZČ</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -26021,6 +26387,8 @@
           <t>NODE_S1989_90_0054</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26035,6 +26403,14 @@
         <is>
           <t>NODE_S1988_89_0062</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>-1.–7. ZČ</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -26214,6 +26590,12 @@
           <t>NODE_S1989_90_0064</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0067</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26228,6 +26610,14 @@
         <is>
           <t>NODE_S1988_89_0071</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -26261,6 +26651,8 @@
           <t>NODE_S1989_90_0064</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26270,6 +26662,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -26684,6 +27084,16 @@
           <t>NODE_S1989_90_0074</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0077</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0078</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26698,6 +27108,14 @@
         <is>
           <t>NODE_S1988_89_0085</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -26731,6 +27149,8 @@
           <t>NODE_S1989_90_0074</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26745,6 +27165,14 @@
         <is>
           <t>NODE_S1988_89_0086</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -26778,6 +27206,8 @@
           <t>NODE_S1989_90_0074</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26792,6 +27222,14 @@
         <is>
           <t>NODE_S1988_89_0087</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>7.–10. ZČ</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -27040,6 +27478,8 @@
           <t>NODE_S1989_90_0080</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27049,6 +27489,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -27270,6 +27718,8 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27284,6 +27734,14 @@
         <is>
           <t>NODE_S1988_89_0097</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -27317,6 +27775,8 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27326,6 +27786,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -27359,6 +27827,8 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27368,6 +27838,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -27636,6 +28114,8 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27645,6 +28125,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -27678,6 +28166,8 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27687,6 +28177,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -27720,6 +28218,8 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27729,6 +28229,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -27762,6 +28270,8 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27771,6 +28281,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -27804,6 +28322,8 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27813,6 +28333,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -27846,6 +28374,8 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27855,6 +28385,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -28029,6 +28567,16 @@
           <t>NODE_S1989_90_0104</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0107</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0108</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28043,6 +28591,14 @@
         <is>
           <t>NODE_S1988_89_0114</t>
         </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -28076,6 +28632,8 @@
           <t>NODE_S1989_90_0104</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28085,6 +28643,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -28118,6 +28684,8 @@
           <t>NODE_S1989_90_0104</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28127,6 +28695,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>5.–10. ZČ</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -28343,6 +28919,8 @@
           <t>NODE_S1989_90_0104</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28352,6 +28930,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="115">
@@ -28631,6 +29217,8 @@
         </is>
       </c>
     </row>
+    <row r="121"/>
+    <row r="122"/>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
@@ -28760,6 +29348,7 @@
         </is>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -756,6 +756,11 @@
           <t>HC Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>44</v>
       </c>
@@ -23666,8 +23671,6 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23723,8 +23726,6 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23780,8 +23781,6 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23837,8 +23836,6 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23894,8 +23891,6 @@
           <t>NODE_S1989_90_0001</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23951,8 +23946,6 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24008,8 +24001,6 @@
           <t>NODE_S1989_90_0007</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24182,7 +24173,6 @@
           <t>NODE_S1989_90_0020</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24373,8 +24363,6 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24435,8 +24423,6 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24492,8 +24478,6 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24549,8 +24533,6 @@
           <t>NODE_S1989_90_0004</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24737,8 +24719,6 @@
           <t>NODE_S1989_90_0026</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25019,8 +24999,6 @@
           <t>NODE_S1989_90_0030</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25076,8 +25054,6 @@
           <t>NODE_S1989_90_0030</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25316,8 +25292,6 @@
           <t>NODE_S1989_90_0037</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25613,8 +25587,6 @@
           <t>NODE_S1989_90_0044</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25670,8 +25642,6 @@
           <t>NODE_S1989_90_0044</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25722,8 +25692,6 @@
           <t>NODE_S1989_90_0046</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25779,8 +25747,6 @@
           <t>NODE_S1989_90_0046</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25831,8 +25797,6 @@
           <t>NODE_S1989_90_0045</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25888,8 +25852,6 @@
           <t>NODE_S1989_90_0045</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25940,8 +25902,6 @@
           <t>NODE_S1989_90_0043</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25992,7 +25952,6 @@
           <t>REG_STC</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>NODE_S1989_90_0057</t>
@@ -26152,8 +26111,6 @@
           <t>NODE_S1989_90_0054</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26387,8 +26344,6 @@
           <t>NODE_S1989_90_0054</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26595,7 +26550,6 @@
           <t>NODE_S1989_90_0067</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26651,8 +26605,6 @@
           <t>NODE_S1989_90_0064</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27149,8 +27101,6 @@
           <t>NODE_S1989_90_0074</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27206,8 +27156,6 @@
           <t>NODE_S1989_90_0074</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27478,8 +27426,6 @@
           <t>NODE_S1989_90_0080</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27718,8 +27664,6 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27775,8 +27719,6 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27827,8 +27769,6 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28114,8 +28054,6 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28166,8 +28104,6 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28218,8 +28154,6 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28270,8 +28204,6 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28322,8 +28254,6 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28374,8 +28304,6 @@
           <t>NODE_S1989_90_0085</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28632,8 +28560,6 @@
           <t>NODE_S1989_90_0104</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28684,8 +28610,6 @@
           <t>NODE_S1989_90_0104</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28919,8 +28843,6 @@
           <t>NODE_S1989_90_0104</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29217,8 +29139,6 @@
         </is>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122"/>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
@@ -29348,7 +29268,6 @@
         </is>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
@@ -57137,7 +57056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57365,6 +57284,18 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>TJ Tesla Liptovský Hrádok se do soutěže nepřihlásila; rezerva Liptovského Mikuláše byla dodatečně zařazena. Z 2. SNHL nikdo nesestoupil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -64310,7 +64310,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M6" t="n">
         <v>4</v>
@@ -64622,13 +64622,13 @@
         <v>6</v>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>21</v>

--- a/data/S1989_90_FINAL.xlsx
+++ b/data/S1989_90_FINAL.xlsx
@@ -29139,6 +29139,8 @@
         </is>
       </c>
     </row>
+    <row r="121"/>
+    <row r="122"/>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
@@ -29268,6 +29270,7 @@
         </is>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
@@ -32934,6 +32937,8 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
